--- a/tables/tab2_decade.xlsx
+++ b/tables/tab2_decade.xlsx
@@ -717,7 +717,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-1923</t>
+          <t>2020-2023</t>
         </is>
       </c>
       <c r="B10" t="n">
